--- a/Dashboard_Vendas.xlsx
+++ b/Dashboard_Vendas.xlsx
@@ -471,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -513,17 +513,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>R$ 265.15</t>
+          <t>R$ 1,162.15</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>R$ 24.10</t>
+          <t>R$ 64.56</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -594,20 +594,20 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>leoa</t>
+          <t>Kauâ Santos</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>08/06/2026 20:31</t>
+          <t>11/06/2026 20:51</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>12</v>
+        <v>25.4</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Prazo/Outros</t>
+          <t>À Vista</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -617,18 +617,18 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Urgente</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Entregue</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -637,16 +637,16 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>leoa</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>08/06/2026 20:30</t>
+          <t>11/06/2026 20:44</t>
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -680,30 +680,30 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>leoa</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>08/06/2026 20:29</t>
+          <t>11/06/2026 19:34</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>20</v>
+        <v>421.8</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Prazo/Outros</t>
+          <t>À Vista</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Retirada</t>
+          <t>Entrega</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Crítico</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -714,7 +714,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -723,16 +723,16 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>kaio</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>08/06/2026 20:01</t>
+          <t>11/06/2026 19:29</t>
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>8.5</v>
+        <v>2</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -766,16 +766,16 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Kauâ Santos</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>08/06/2026 19:39</t>
+          <t>09/06/2026 21:02</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -809,20 +809,20 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Kauâ Santos</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>02/06/2026 20:02</t>
+          <t>09/06/2026 21:01</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>76.5</v>
+        <v>14</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>À Vista</t>
+          <t>Prazo/Outros</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -843,7 +843,7 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -852,16 +852,16 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>leoa</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>02/06/2026 20:02</t>
+          <t>09/06/2026 21:00</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>55.35</v>
+        <v>421.8</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
@@ -870,12 +870,12 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Retirada</t>
+          <t>Entrega</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Crítico</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -886,7 +886,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -895,16 +895,16 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>leoa</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 21:14</t>
+          <t>08/06/2026 20:31</t>
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Retirada</t>
+          <t>Entrega</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -923,13 +923,13 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Entregue</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -938,41 +938,41 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>leoa</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 20:36</t>
+          <t>08/06/2026 20:30</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>36.8</v>
+        <v>10</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>À Vista</t>
+          <t>Prazo/Outros</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Entrega</t>
+          <t>Retirada</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Crítico</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Entregue</t>
+          <t>Pendente</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>leoa</t>
+          <t>leoaa</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>29/05/2026 20:35</t>
+          <t>08/06/2026 20:29</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
@@ -1015,42 +1015,343 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>kaio</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>08/06/2026 20:01</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Prazo/Outros</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Retirada</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Kauâ Santos</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>08/06/2026 19:39</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Prazo/Outros</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Retirada</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Kauâ Santos</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>02/06/2026 20:02</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>À Vista</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Retirada</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>leoaa</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>02/06/2026 20:02</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>À Vista</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Retirada</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>leoaa</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>29/05/2026 21:14</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Prazo/Outros</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Retirada</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>leoaa</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>29/05/2026 20:36</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>À Vista</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Entregue</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>leoaa</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>29/05/2026 20:35</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Prazo/Outros</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Retirada</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Vendedor Padrão</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>leoa</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Vendedor Padrão</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>leoaa</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>29/05/2026 20:31</t>
         </is>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E26" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Prazo/Outros</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G26" s="7" t="inlineStr">
         <is>
           <t>Retirada</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
